--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>5.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.22</v>
+        <v>9.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
-        <v>5.05</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>9.4</v>
+        <v>5.22</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="M24" t="n">
-        <v>3.87</v>
+        <v>3.48</v>
       </c>
       <c r="N24" t="n">
-        <v>6.69</v>
+        <v>3.48</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="M25" t="n">
-        <v>3.48</v>
+        <v>3.87</v>
       </c>
       <c r="N25" t="n">
-        <v>3.48</v>
+        <v>6.69</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>2.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>3.28</v>
       </c>
       <c r="N21" t="n">
-        <v>5.22</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.66</v>
+        <v>1.61</v>
       </c>
       <c r="M22" t="n">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>5.22</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>3.48</v>
+        <v>3.87</v>
       </c>
       <c r="N24" t="n">
-        <v>3.48</v>
+        <v>6.69</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="M25" t="n">
-        <v>3.87</v>
+        <v>3.48</v>
       </c>
       <c r="N25" t="n">
-        <v>6.69</v>
+        <v>3.48</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>8.6</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>5.04</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
-        <v>5.05</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>9.4</v>
+        <v>5.22</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.76</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
-        <v>3.54</v>
+        <v>5.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1.74</v>
+        <v>9.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.66</v>
+        <v>4.76</v>
       </c>
       <c r="M21" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="N21" t="n">
-        <v>2.56</v>
+        <v>1.74</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.61</v>
+        <v>2.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>3.28</v>
       </c>
       <c r="N22" t="n">
-        <v>5.22</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>5.04</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>8.6</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.31</v>
+        <v>2.66</v>
       </c>
       <c r="M20" t="n">
-        <v>5.05</v>
+        <v>3.28</v>
       </c>
       <c r="N20" t="n">
-        <v>9.4</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.76</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.54</v>
+        <v>5.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.74</v>
+        <v>9.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.66</v>
+        <v>4.76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>1.74</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>8.6</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>5.04</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5625</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>5.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.22</v>
+        <v>9.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.66</v>
+        <v>1.61</v>
       </c>
       <c r="M20" t="n">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>5.22</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>4.76</v>
       </c>
       <c r="M21" t="n">
-        <v>5.05</v>
+        <v>3.54</v>
       </c>
       <c r="N21" t="n">
-        <v>9.4</v>
+        <v>1.74</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.76</v>
+        <v>2.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="N22" t="n">
-        <v>1.74</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5625</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>2.66</v>
       </c>
       <c r="M19" t="n">
-        <v>5.05</v>
+        <v>3.28</v>
       </c>
       <c r="N19" t="n">
-        <v>9.4</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
-        <v>3.92</v>
+        <v>5.05</v>
       </c>
       <c r="N20" t="n">
-        <v>5.22</v>
+        <v>9.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.76</v>
+        <v>1.61</v>
       </c>
       <c r="M21" t="n">
-        <v>3.54</v>
+        <v>3.92</v>
       </c>
       <c r="N21" t="n">
-        <v>1.74</v>
+        <v>5.22</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.66</v>
+        <v>4.76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>1.74</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>5.04</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>8.6</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5625</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.66</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.28</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>5.22</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.61</v>
+        <v>4.76</v>
       </c>
       <c r="M21" t="n">
-        <v>3.92</v>
+        <v>3.54</v>
       </c>
       <c r="N21" t="n">
-        <v>5.22</v>
+        <v>1.74</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.76</v>
+        <v>2.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="N22" t="n">
-        <v>1.74</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="M24" t="n">
-        <v>3.87</v>
+        <v>3.48</v>
       </c>
       <c r="N24" t="n">
-        <v>6.69</v>
+        <v>3.48</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="M25" t="n">
-        <v>3.48</v>
+        <v>3.87</v>
       </c>
       <c r="N25" t="n">
-        <v>3.48</v>
+        <v>6.69</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>8.6</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>5.04</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5625</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.31</v>
+        <v>2.66</v>
       </c>
       <c r="M20" t="n">
-        <v>5.05</v>
+        <v>3.28</v>
       </c>
       <c r="N20" t="n">
-        <v>9.4</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.66</v>
+        <v>1.31</v>
       </c>
       <c r="M22" t="n">
-        <v>3.28</v>
+        <v>5.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>9.4</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>5.04</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>8.6</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>5.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.22</v>
+        <v>9.4</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.66</v>
+        <v>4.76</v>
       </c>
       <c r="M20" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="N20" t="n">
-        <v>2.56</v>
+        <v>1.74</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.76</v>
+        <v>2.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="N21" t="n">
-        <v>1.74</v>
+        <v>2.56</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="M22" t="n">
-        <v>5.05</v>
+        <v>3.92</v>
       </c>
       <c r="N22" t="n">
-        <v>9.4</v>
+        <v>5.22</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>5.04</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>8.6</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>5.04</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5625</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5625</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="M19" t="n">
-        <v>5.05</v>
+        <v>3.92</v>
       </c>
       <c r="N19" t="n">
-        <v>9.4</v>
+        <v>5.22</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.76</v>
+        <v>2.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="N20" t="n">
-        <v>1.74</v>
+        <v>2.56</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.66</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>3.28</v>
+        <v>5.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.56</v>
+        <v>9.4</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.61</v>
+        <v>4.76</v>
       </c>
       <c r="M22" t="n">
-        <v>3.92</v>
+        <v>3.54</v>
       </c>
       <c r="N22" t="n">
-        <v>5.22</v>
+        <v>1.74</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,17 +1131,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46057.48958333334</v>
+        <v>46057.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46057.5</v>
+        <v>46057.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46057.5</v>
+        <v>46057.48958333334</v>
       </c>
     </row>
     <row r="11">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.75</v>
+        <v>3.19</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="N12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>10</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.55</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46057.54166666666</v>
+        <v>46057.5</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46057.5625</v>
+        <v>46057.5</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46057.5625</v>
+        <v>46057.5</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,80 +2202,80 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>2.52</v>
       </c>
       <c r="O15" t="n">
-        <v>2.52</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
         <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
         <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH15" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AI15" s="3" t="n">
-        <v>46057.58333333334</v>
+        <v>46057.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46057.625</v>
+        <v>46057.5625</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.07</v>
+        <v>8.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.34</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46057.64583333334</v>
+        <v>46057.5625</v>
       </c>
     </row>
     <row r="18">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.07</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
         <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>3.13</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.45</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.41</v>
+        <v>2.11</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.66</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46057.6875</v>
+        <v>46057.58333333334</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.61</v>
+        <v>5.86</v>
       </c>
       <c r="M19" t="n">
-        <v>3.92</v>
+        <v>3.47</v>
       </c>
       <c r="N19" t="n">
-        <v>5.22</v>
+        <v>1.58</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46057.69791666666</v>
+        <v>46057.625</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,76 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.66</v>
+        <v>3.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
         <v>2.56</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46057.69791666666</v>
+        <v>46057.64583333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>5.05</v>
+        <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>9.4</v>
+        <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46057.69791666666</v>
+        <v>46057.6875</v>
       </c>
     </row>
     <row r="22">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.3</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>5.05</v>
       </c>
       <c r="N23" t="n">
-        <v>1.56</v>
+        <v>9.4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46057.70833333334</v>
+        <v>46057.69791666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,27 +3236,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.14</v>
+        <v>2.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="N24" t="n">
-        <v>3.48</v>
+        <v>2.56</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46057.79166666666</v>
+        <v>46057.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3355,27 +3355,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M25" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="N25" t="n">
-        <v>6.69</v>
+        <v>5.22</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>46057.79166666666</v>
+        <v>46057.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3474,27 +3474,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.64</v>
+        <v>5.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.17</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.88</v>
+        <v>1.56</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3584,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46057.83333333334</v>
+        <v>46057.70833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="M27" t="n">
         <v>3.48</v>
       </c>
       <c r="N27" t="n">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46057.83333333334</v>
+        <v>46057.79166666666</v>
       </c>
     </row>
     <row r="28">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.87</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>6.69</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46057.89583333334</v>
+        <v>46057.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -3831,116 +3831,473 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46057.83333333334</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3" t="n">
+        <v>46057.83333333334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3" t="n">
+        <v>46057.89583333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>Palmeiras</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Vitória</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="L32" t="n">
         <v>1.37</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M32" t="n">
         <v>5.04</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N32" t="n">
         <v>8.6</v>
       </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="n">
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="P5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.77</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V5" t="n">
-        <v>13</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AF5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC5" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>2.74</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>2.61</v>
       </c>
       <c r="P8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.98</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.96</v>
+        <v>3.19</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="N11" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.3</v>
       </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.44</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="Z11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.55</v>
       </c>
-      <c r="AA11" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
         <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
         <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>4.34</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
         <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>1.7</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
         <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="P21" t="n">
         <v>2.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="U21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V21" t="n">
-        <v>4.7</v>
+        <v>5.26</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="n">
         <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
         <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46057.6875</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.76</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>1.74</v>
+        <v>5.25</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="N23" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.66</v>
+        <v>4.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.56</v>
+        <v>1.82</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.61</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>5.22</v>
+        <v>2.55</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="M26" t="n">
         <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46057.70833333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="O8" t="n">
-        <v>2.61</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.74</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.71</v>
+        <v>2.08</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.98</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="N22" t="n">
-        <v>5.25</v>
+        <v>10</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="R22" t="n">
         <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.47</v>
       </c>
-      <c r="V22" t="n">
-        <v>6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AE22" t="n">
         <v>2</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.35</v>
+        <v>3.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O23" t="n">
         <v>4.8</v>
       </c>
-      <c r="N23" t="n">
-        <v>10</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.7</v>
-      </c>
       <c r="P23" t="n">
-        <v>2.41</v>
+        <v>2.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>2.46</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.4</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.32</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>4.8</v>
+        <v>3.62</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.46</v>
+        <v>3.07</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
         <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.55</v>
       </c>
-      <c r="O25" t="n">
+      <c r="U25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3.62</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AA25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC25" t="n">
-        <v>3.24</v>
+        <v>2.76</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="M27" t="n">
-        <v>3.48</v>
+        <v>3.87</v>
       </c>
       <c r="N27" t="n">
-        <v>3.48</v>
+        <v>6.69</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="M28" t="n">
-        <v>3.87</v>
+        <v>3.48</v>
       </c>
       <c r="N28" t="n">
-        <v>6.69</v>
+        <v>3.48</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.64</v>
+        <v>2.19</v>
       </c>
       <c r="M29" t="n">
-        <v>3.17</v>
+        <v>3.48</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>3.36</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="M30" t="n">
-        <v>3.48</v>
+        <v>3.17</v>
       </c>
       <c r="N30" t="n">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.61</v>
+        <v>3.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.74</v>
+        <v>3.15</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>3.98</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.71</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.98</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
         <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
         <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46057.54166666666</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="M16" t="n">
         <v>4.2</v>
@@ -2340,7 +2340,7 @@
         <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.35</v>
@@ -2370,7 +2370,7 @@
         <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
         <v>1.85</v>
@@ -2566,7 +2566,7 @@
         <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
         <v>3.7</v>
@@ -2801,22 +2801,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="O20" t="n">
-        <v>3.91</v>
+        <v>3.55</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="R20" t="n">
         <v>1.44</v>
@@ -2825,10 +2825,10 @@
         <v>2.56</v>
       </c>
       <c r="T20" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
         <v>6.5</v>
@@ -2843,19 +2843,19 @@
         <v>1.32</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC20" t="n">
         <v>3.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE20" t="n">
         <v>1.83</v>
@@ -2864,7 +2864,7 @@
         <v>1.87</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
         <v>1.33</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>5.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="R22" t="n">
         <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="U22" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.15</v>
+        <v>3.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.32</v>
+        <v>2.35</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>3.62</v>
       </c>
       <c r="P23" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.46</v>
+        <v>3.07</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
         <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="O24" t="n">
-        <v>3.62</v>
+        <v>4.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.07</v>
+        <v>2.46</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.85</v>
       </c>
       <c r="U24" t="n">
         <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="N25" t="n">
-        <v>5.25</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
         <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.47</v>
       </c>
-      <c r="V25" t="n">
-        <v>6</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AE25" t="n">
         <v>2</v>
       </c>
-      <c r="AC25" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.35</v>
+        <v>3.32</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.87</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>6.69</v>
+        <v>7.1</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="M29" t="n">
-        <v>3.48</v>
+        <v>3.17</v>
       </c>
       <c r="N29" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="M31" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.75</v>
+        <v>8.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>5.04</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>8.6</v>
+        <v>3.77</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -1025,7 +1025,7 @@
         <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="P5" t="n">
         <v>1.95</v>
@@ -1037,19 +1037,19 @@
         <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
         <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
         <v>1.08</v>
@@ -1079,7 +1079,7 @@
         <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
         <v>1.98</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.77</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AF7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC7" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>4.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>2.11</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>6.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2206,40 +2206,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
         <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
         <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.02</v>
@@ -2248,19 +2248,19 @@
         <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
         <v>1.77</v>
@@ -2269,10 +2269,10 @@
         <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46057.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -2694,13 +2694,13 @@
         <v>6.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
         <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
         <v>2.47</v>
@@ -2724,10 +2724,10 @@
         <v>1.34</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AB19" t="n">
         <v>1.63</v>
@@ -2739,13 +2739,13 @@
         <v>1.19</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF19" t="n">
         <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
         <v>1.07</v>
@@ -2804,25 +2804,25 @@
         <v>3.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.55</v>
+        <v>3.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T20" t="n">
         <v>3.05</v>
@@ -2831,10 +2831,10 @@
         <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>4.06</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>5.25</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.4</v>
+        <v>2.48</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.62</v>
+        <v>3.24</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.35</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>5.25</v>
       </c>
       <c r="O23" t="n">
-        <v>3.62</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.07</v>
+        <v>5.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="V23" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB23" t="n">
         <v>2</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.46</v>
+        <v>3.06</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
         <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="N25" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
         <v>2.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="R25" t="n">
         <v>1.32</v>
@@ -3429,7 +3429,7 @@
         <v>5.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3453,13 +3453,13 @@
         <v>1.47</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF25" t="n">
         <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
         <v>3.32</v>
@@ -3518,7 +3518,7 @@
         <v>5.35</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
         <v>1.57</v>
@@ -3527,55 +3527,55 @@
         <v>4.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q26" t="n">
         <v>2.06</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="T26" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
         <v>1.59</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC26" t="n">
         <v>2.32</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AG26" t="n">
         <v>1.21</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.16</v>
+        <v>2.76</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AB29" t="n">
         <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE29" t="n">
         <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.8</v>
       </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2.06</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
         <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE30" t="n">
         <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.57</v>
+        <v>3.27</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.74</v>
+        <v>4.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="P9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.77</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AF9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC9" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.06</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.48</v>
+        <v>3.06</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
         <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="N23" t="n">
-        <v>5.25</v>
+        <v>10</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.4</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.47</v>
       </c>
-      <c r="V23" t="n">
-        <v>6</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.28</v>
+        <v>3.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>5.25</v>
       </c>
       <c r="O24" t="n">
-        <v>3.64</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.06</v>
+        <v>5.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="V24" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.12</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.56</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.31</v>
+        <v>4.06</v>
       </c>
       <c r="M25" t="n">
-        <v>4.95</v>
+        <v>3.41</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>1.75</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.449999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC25" t="n">
         <v>3.4</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.15</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.32</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="M31" t="n">
-        <v>4.75</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>8.6</v>
+        <v>3.77</v>
       </c>
       <c r="O31" t="n">
-        <v>1.83</v>
+        <v>2.96</v>
       </c>
       <c r="P31" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.2</v>
+        <v>4.35</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>2.44</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF31" t="n">
         <v>2</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AG31" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.08</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
-        <v>2.95</v>
+        <v>4.75</v>
       </c>
       <c r="N32" t="n">
-        <v>3.77</v>
+        <v>8.6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.96</v>
+        <v>1.83</v>
       </c>
       <c r="P32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE32" t="n">
         <v>2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z32" t="n">
+      <c r="AF32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH32" t="n">
         <v>3.08</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.57</v>
+        <v>3.27</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.74</v>
+        <v>4.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S8" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>4.06</v>
       </c>
       <c r="M23" t="n">
-        <v>4.95</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>10</v>
+        <v>1.75</v>
       </c>
       <c r="O23" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.449999999999999</v>
+        <v>2.48</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.4</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.87</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.32</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.06</v>
+        <v>1.31</v>
       </c>
       <c r="M25" t="n">
-        <v>3.41</v>
+        <v>4.95</v>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>10</v>
       </c>
       <c r="O25" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.48</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>2.73</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="V25" t="n">
-        <v>6.45</v>
+        <v>5.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.24</v>
+        <v>4.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.87</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>3.32</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>7.1</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF27" t="n">
         <v>1.93</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.72</v>
+        <v>1.66</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.86</v>
+        <v>1.93</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>5.13</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.12</v>
+        <v>3.54</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>2.72</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.8</v>
       </c>
-      <c r="M29" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P29" t="n">
+      <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AA29" t="n">
         <v>2.06</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.23</v>
       </c>
       <c r="AB29" t="n">
         <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.78</v>
+        <v>3.54</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE29" t="n">
         <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V30" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.16</v>
+        <v>2.76</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
         <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE30" t="n">
         <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="M31" t="n">
-        <v>2.95</v>
+        <v>4.75</v>
       </c>
       <c r="N31" t="n">
-        <v>3.77</v>
+        <v>8.6</v>
       </c>
       <c r="O31" t="n">
-        <v>2.96</v>
+        <v>1.83</v>
       </c>
       <c r="P31" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE31" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="AF31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH31" t="n">
         <v>3.08</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="M32" t="n">
-        <v>4.75</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>8.6</v>
+        <v>3.77</v>
       </c>
       <c r="O32" t="n">
-        <v>1.83</v>
+        <v>2.96</v>
       </c>
       <c r="P32" t="n">
-        <v>2.56</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.2</v>
+        <v>4.35</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>3.04</v>
+        <v>2.44</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U32" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF32" t="n">
         <v>2</v>
       </c>
-      <c r="AF32" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.08</v>
+        <v>1.64</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.15</v>
+        <v>4.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>2.11</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>7.3</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>6.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.77</v>
+        <v>2.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,49 +2206,49 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="O15" t="n">
         <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T15" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.14</v>
+        <v>3.37</v>
       </c>
       <c r="AA15" t="n">
         <v>1.96</v>
@@ -2263,13 +2263,13 @@
         <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
         <v>1.29</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -2559,17 +2559,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="O18" t="n">
         <v>2.41</v>
@@ -2810,13 +2810,13 @@
         <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
         <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="R20" t="n">
         <v>1.38</v>
@@ -2831,7 +2831,7 @@
         <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>6.75</v>
+        <v>7.8</v>
       </c>
       <c r="W20" t="n">
         <v>1.07</v>
@@ -2846,22 +2846,22 @@
         <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC20" t="n">
         <v>3.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG20" t="n">
         <v>1.32</v>
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.06</v>
+        <v>2.99</v>
       </c>
       <c r="R22" t="n">
         <v>1.42</v>
@@ -3075,19 +3075,19 @@
         <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
         <v>3.12</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
         <v>3.24</v>
@@ -3099,13 +3099,13 @@
         <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3158,19 +3158,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="O23" t="n">
         <v>4.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.07</v>
       </c>
       <c r="Q23" t="n">
         <v>2.48</v>
@@ -3197,10 +3197,10 @@
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
         <v>1.96</v>
@@ -3209,22 +3209,22 @@
         <v>1.86</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
         <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>5.25</v>
+        <v>5.45</v>
       </c>
       <c r="O24" t="n">
         <v>2.1</v>
@@ -3292,7 +3292,7 @@
         <v>2.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
         <v>1.35</v>
@@ -3304,7 +3304,7 @@
         <v>2.59</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
         <v>6</v>
@@ -3313,37 +3313,37 @@
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA24" t="n">
         <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG24" t="n">
         <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O25" t="n">
         <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.449999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="R25" t="n">
         <v>1.32</v>
@@ -3420,19 +3420,19 @@
         <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
         <v>1.16</v>
@@ -3447,10 +3447,10 @@
         <v>2.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE25" t="n">
         <v>1.99</v>
@@ -3459,7 +3459,7 @@
         <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AH25" t="n">
         <v>3.32</v>
@@ -3515,34 +3515,34 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.35</v>
+        <v>5.39</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O26" t="n">
         <v>4.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="R26" t="n">
         <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="T26" t="n">
         <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
         <v>4.95</v>
@@ -3554,16 +3554,16 @@
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="AA26" t="n">
         <v>1.59</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
         <v>2.32</v>
@@ -3572,16 +3572,16 @@
         <v>1.49</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AG26" t="n">
         <v>1.21</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46057.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.86</v>
+        <v>1.93</v>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>5.13</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
       <c r="T27" t="n">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.12</v>
+        <v>3.87</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.66</v>
+        <v>2.58</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>7.1</v>
+        <v>3.31</v>
       </c>
       <c r="O28" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.13</v>
+        <v>3.94</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>2.57</v>
+        <v>2.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.54</v>
+        <v>3.12</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.72</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3872,22 +3872,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.7</v>
+        <v>3.93</v>
       </c>
       <c r="O29" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="P29" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="R29" t="n">
         <v>1.46</v>
@@ -3908,13 +3908,13 @@
         <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
         <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="AA29" t="n">
         <v>2.06</v>
@@ -3929,16 +3929,16 @@
         <v>1.23</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3991,16 +3991,16 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>3.64</v>
       </c>
       <c r="P30" t="n">
         <v>2.06</v>
@@ -4018,7 +4018,7 @@
         <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
         <v>8.5</v>
@@ -4030,7 +4030,7 @@
         <v>1.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="Z30" t="n">
         <v>2.76</v>
@@ -4039,7 +4039,7 @@
         <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC30" t="n">
         <v>3.78</v>
@@ -4057,7 +4057,7 @@
         <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4110,31 +4110,31 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
         <v>1.83</v>
       </c>
       <c r="P31" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
         <v>7.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
         <v>3.04</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U31" t="n">
         <v>1.46</v>
@@ -4161,13 +4161,13 @@
         <v>2.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AD31" t="n">
         <v>1.35</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AF31" t="n">
         <v>1.69</v>
@@ -4176,7 +4176,7 @@
         <v>1.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="M32" t="n">
         <v>2.95</v>
@@ -4238,22 +4238,22 @@
         <v>3.77</v>
       </c>
       <c r="O32" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.35</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
         <v>2.44</v>
       </c>
       <c r="T32" t="n">
-        <v>2.63</v>
+        <v>2.94</v>
       </c>
       <c r="U32" t="n">
         <v>1.35</v>
@@ -4277,7 +4277,7 @@
         <v>2.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC32" t="n">
         <v>3.3</v>
@@ -4286,13 +4286,13 @@
         <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH32" t="n">
         <v>1.64</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>2.57</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>5.74</v>
       </c>
       <c r="R7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.44</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46057.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="N13" t="n">
         <v>2.43</v>
       </c>
       <c r="O13" t="n">
-        <v>4.34</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
         <v>1.76</v>
@@ -1986,10 +1986,10 @@
         <v>3.27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
         <v>3.48</v>
@@ -1998,19 +1998,19 @@
         <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="AA13" t="n">
         <v>2.46</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>1.58</v>
       </c>
       <c r="O19" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="P19" t="n">
         <v>2.18</v>
@@ -2700,16 +2700,16 @@
         <v>2.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="T19" t="n">
         <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
         <v>8.1</v>
@@ -2718,7 +2718,7 @@
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
         <v>1.34</v>
@@ -2733,7 +2733,7 @@
         <v>1.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
         <v>1.19</v>
@@ -2745,10 +2745,10 @@
         <v>1.64</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46057.625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="O22" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.99</v>
+        <v>2.48</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
         <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>6.7</v>
+        <v>6.45</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.48</v>
+        <v>2.99</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
         <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>5.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="P24" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.59</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH24" t="n">
-        <v>2.31</v>
+        <v>3.32</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>9.800000000000001</v>
+        <v>5.45</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.7</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="T25" t="n">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="U25" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.32</v>
+        <v>2.31</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>3.93</v>
+        <v>2.55</v>
       </c>
       <c r="O29" t="n">
-        <v>2.45</v>
+        <v>3.64</v>
       </c>
       <c r="P29" t="n">
         <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.13</v>
+        <v>2.76</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.55</v>
+        <v>3.93</v>
       </c>
       <c r="O30" t="n">
-        <v>3.64</v>
+        <v>2.45</v>
       </c>
       <c r="P30" t="n">
         <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="R30" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.34</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>3.77</v>
       </c>
       <c r="O31" t="n">
-        <v>1.83</v>
+        <v>2.94</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>2.44</v>
       </c>
       <c r="T31" t="n">
-        <v>2.53</v>
+        <v>2.94</v>
       </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="AA31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.78</v>
       </c>
-      <c r="AB31" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AC31" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.95</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="M32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH32" t="n">
         <v>2.95</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>3.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.74</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.71</v>
+        <v>2.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>2.57</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>5.74</v>
       </c>
       <c r="R8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.44</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>5.34</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>7.02</v>
       </c>
       <c r="O16" t="n">
-        <v>7</v>
+        <v>1.81</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>6.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.17</v>
+        <v>1.92</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>2.21</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.08</v>
+        <v>3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>5.34</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>7.02</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.92</v>
+        <v>3.17</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.48</v>
+        <v>2.99</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
         <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.99</v>
+        <v>6.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.05</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>3.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.33</v>
       </c>
-      <c r="M24" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.32</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>6.5</v>
+        <v>3.31</v>
       </c>
       <c r="O27" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.13</v>
+        <v>3.94</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.02</v>
+        <v>2.69</v>
       </c>
       <c r="T27" t="n">
-        <v>2.57</v>
+        <v>2.94</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.87</v>
+        <v>3.12</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.34</v>
       </c>
-      <c r="AE27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH27" t="n">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="N28" t="n">
-        <v>3.31</v>
+        <v>6.5</v>
       </c>
       <c r="O28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
         <v>2.8</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.44</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>2.58</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.55</v>
+        <v>3.93</v>
       </c>
       <c r="O29" t="n">
-        <v>3.64</v>
+        <v>2.45</v>
       </c>
       <c r="P29" t="n">
         <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.34</v>
       </c>
-      <c r="V29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>3.93</v>
+        <v>2.55</v>
       </c>
       <c r="O30" t="n">
-        <v>2.45</v>
+        <v>3.64</v>
       </c>
       <c r="P30" t="n">
         <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.13</v>
+        <v>2.76</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="M31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N31" t="n">
+        <v>8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH31" t="n">
         <v>2.95</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.64</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.36</v>
+        <v>2.27</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>2.95</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>3.77</v>
       </c>
       <c r="O32" t="n">
-        <v>1.83</v>
+        <v>2.94</v>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>3.04</v>
+        <v>2.44</v>
       </c>
       <c r="T32" t="n">
-        <v>2.53</v>
+        <v>2.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.62</v>
+        <v>3.08</v>
       </c>
       <c r="AA32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.78</v>
       </c>
-      <c r="AB32" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AC32" t="n">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.95</v>
+        <v>1.64</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>2.57</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>5.74</v>
       </c>
       <c r="R7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.44</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.57</v>
+        <v>3.32</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.74</v>
+        <v>4.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.28</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.03</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC9" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.99</v>
+        <v>6.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.05</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>3.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.33</v>
       </c>
-      <c r="M23" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.32</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="P24" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.48</v>
+        <v>2.99</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
         <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>3.93</v>
+        <v>2.55</v>
       </c>
       <c r="O29" t="n">
-        <v>2.45</v>
+        <v>3.64</v>
       </c>
       <c r="P29" t="n">
         <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.13</v>
+        <v>2.76</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.54</v>
+        <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.55</v>
+        <v>3.93</v>
       </c>
       <c r="O30" t="n">
-        <v>3.64</v>
+        <v>2.45</v>
       </c>
       <c r="P30" t="n">
         <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="R30" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.34</v>
       </c>
-      <c r="V30" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>4.62</v>
+        <v>2.57</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>5.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>4</v>
+        <v>2.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>2.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.39</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1144,64 +1144,64 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>3.24</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.74</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.71</v>
+        <v>2.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>4.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>4.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="Z9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2.88</v>
       </c>
-      <c r="AA9" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>6.05</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.33</v>
       </c>
-      <c r="M22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.32</v>
+        <v>1.21</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.9</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>1.91</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.48</v>
+        <v>6.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.73</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>3.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="N27" t="n">
-        <v>3.31</v>
+        <v>6.5</v>
       </c>
       <c r="O27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.8</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.44</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.66</v>
+        <v>2.58</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>6.5</v>
+        <v>3.31</v>
       </c>
       <c r="O28" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.13</v>
+        <v>3.94</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>2.57</v>
+        <v>2.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.87</v>
+        <v>3.12</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>3.44</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG28" t="n">
         <v>1.34</v>
       </c>
-      <c r="AE28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH28" t="n">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.9</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>1.91</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.48</v>
+        <v>6.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.96</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.21</v>
+        <v>3.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.33</v>
       </c>
-      <c r="M23" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.32</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>5.45</v>
       </c>
       <c r="O24" t="n">
-        <v>3.45</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.99</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.05</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>2.31</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>5.45</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.9</v>
+        <v>2.99</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.31</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O6" t="n">
         <v>4.62</v>
@@ -1159,10 +1159,10 @@
         <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V6" t="n">
         <v>5.8</v>
@@ -1177,25 +1177,25 @@
         <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
         <v>2.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
         <v>1.62</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG6" t="n">
         <v>1.19</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>3.81</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.64</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="O5" t="n">
-        <v>2.57</v>
+        <v>4.62</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.74</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>2.27</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.29</v>
+        <v>3.98</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AE5" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>3.24</v>
+        <v>2.57</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>5.74</v>
       </c>
       <c r="R7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.44</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>8.5</v>
       </c>
       <c r="M16" t="n">
-        <v>5.34</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>7.02</v>
+        <v>1.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.81</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.05</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>3.04</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2.69</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.2</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>1.08</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>5.34</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>7.02</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>1.81</v>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>6.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.17</v>
+        <v>1.92</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>2.21</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.33</v>
       </c>
-      <c r="M22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.32</v>
+        <v>1.21</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.48</v>
+        <v>2.99</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
         <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>6.45</v>
+        <v>6.7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.99</v>
+        <v>6.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="V25" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="W25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.05</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>3.32</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.81</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>3.64</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>4.62</v>
+        <v>2.57</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>5.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.98</v>
+        <v>2.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.69</v>
+        <v>2.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.62</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.83</v>
+        <v>3.81</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>2.57</v>
+        <v>4.62</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.74</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>2.27</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.29</v>
+        <v>3.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AE7" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1971,70 +1971,70 @@
         <v>2.87</v>
       </c>
       <c r="M13" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="T13" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.5</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>5.34</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>7.02</v>
       </c>
       <c r="O16" t="n">
-        <v>7</v>
+        <v>1.81</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.8</v>
+        <v>6.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.69</v>
+        <v>2.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.17</v>
+        <v>1.92</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>2.21</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.08</v>
+        <v>3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.28</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>5.34</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>7.02</v>
+        <v>1.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.81</v>
+        <v>7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.05</v>
+        <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4</v>
+        <v>3.04</v>
       </c>
       <c r="T17" t="n">
-        <v>2.05</v>
+        <v>2.69</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="V17" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.2</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>1.91</v>
+        <v>5.45</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.48</v>
+        <v>4.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.4</v>
       </c>
-      <c r="V22" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.21</v>
+        <v>2.31</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.99</v>
+        <v>6.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="V23" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="W23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.05</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>3.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>5.45</v>
+        <v>1.91</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.9</v>
+        <v>2.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="T24" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.31</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>9.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V25" t="n">
         <v>6.7</v>
       </c>
-      <c r="R25" t="n">
+      <c r="W25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.32</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AH25" t="n">
-        <v>3.32</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.57</v>
+        <v>3.32</v>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.74</v>
+        <v>4.28</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.29</v>
+        <v>2.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.54</v>
+        <v>3.81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="N8" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24</v>
+        <v>4.62</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>2.56</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="V8" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>3.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.08</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.28</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>4.1</v>
+        <v>2.99</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="V9" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.03</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.32</v>
       </c>
-      <c r="AC9" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>5.34</v>
+        <v>4.75</v>
       </c>
       <c r="N16" t="n">
-        <v>7.02</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.05</v>
+        <v>5.75</v>
       </c>
       <c r="R16" t="n">
         <v>1.19</v>
@@ -2349,10 +2349,10 @@
         <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V16" t="n">
         <v>4.2</v>
@@ -2376,22 +2376,22 @@
         <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="n">
         <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
         <v>1.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="T17" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
         <v>1.05</v>
@@ -2489,13 +2489,13 @@
         <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB17" t="n">
         <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.17</v>
+        <v>3.44</v>
       </c>
       <c r="AD17" t="n">
         <v>1.3</v>
@@ -2504,7 +2504,7 @@
         <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG17" t="n">
         <v>1.2</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
         <v>3.7</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46057.58333333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V22" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.6</v>
       </c>
-      <c r="M22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AB22" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.31</v>
+        <v>3.45</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.33</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>9.800000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
-        <v>1.7</v>
+        <v>3.39</v>
       </c>
       <c r="P23" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.7</v>
+        <v>2.69</v>
       </c>
       <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>3.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O24" t="n">
         <v>4.8</v>
@@ -3292,40 +3292,40 @@
         <v>2.07</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
         <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AA24" t="n">
         <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>3.3</v>
@@ -3334,16 +3334,16 @@
         <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
         <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.12</v>
+        <v>3.62</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB25" t="n">
         <v>2</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AC25" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>2.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.39</v>
+        <v>6.1</v>
       </c>
       <c r="M26" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.21</v>
+        <v>2.45</v>
       </c>
       <c r="AH26" t="n">
         <v>1.12</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.42</v>
       </c>
-      <c r="M27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.33</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH27" t="n">
-        <v>2.58</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3.31</v>
+        <v>7.25</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.94</v>
+        <v>6.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.69</v>
+        <v>3.02</v>
       </c>
       <c r="T28" t="n">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.12</v>
+        <v>3.92</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.66</v>
+        <v>2.63</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3872,16 +3872,16 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
         <v>2.06</v>
@@ -3890,46 +3890,46 @@
         <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
         <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
         <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
         <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AA29" t="n">
         <v>2.23</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC29" t="n">
         <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
         <v>1.85</v>
@@ -3991,34 +3991,34 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.93</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="R30" t="n">
         <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
         <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
         <v>7.5</v>
@@ -4027,37 +4027,37 @@
         <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
         <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AA30" t="n">
         <v>2.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>8.44</v>
       </c>
       <c r="O31" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.2</v>
+        <v>8.31</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W31" t="n">
         <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4229,28 +4229,28 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="N32" t="n">
-        <v>3.77</v>
+        <v>3.44</v>
       </c>
       <c r="O32" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="T32" t="n">
         <v>2.94</v>
@@ -4259,25 +4259,25 @@
         <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
         <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
         <v>3.3</v>
@@ -4286,16 +4286,16 @@
         <v>1.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1144,19 +1144,19 @@
         <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.74</v>
+        <v>5.24</v>
       </c>
       <c r="R6" t="n">
         <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="T6" t="n">
         <v>3.4</v>
@@ -1174,13 +1174,13 @@
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AB6" t="n">
         <v>1.44</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.81</v>
+        <v>2.54</v>
       </c>
       <c r="M8" t="n">
-        <v>3.64</v>
+        <v>3.12</v>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>2.74</v>
       </c>
       <c r="O8" t="n">
-        <v>4.62</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="N9" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="T9" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.07</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="N10" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="O10" t="n">
-        <v>5.76</v>
+        <v>5.82</v>
       </c>
       <c r="P10" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
         <v>2.11</v>
@@ -1653,31 +1653,31 @@
         <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
         <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
         <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46057.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
         <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46057.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V16" t="n">
         <v>6.5</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.85</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.29</v>
+        <v>5.75</v>
       </c>
       <c r="O17" t="n">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>2.73</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.44</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.08</v>
+        <v>3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.86</v>
+        <v>5.57</v>
       </c>
       <c r="M19" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="O19" t="n">
-        <v>6.4</v>
+        <v>6.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W19" t="n">
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46057.625</v>
@@ -2804,70 +2804,70 @@
         <v>3.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.38</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V20" t="n">
-        <v>7.8</v>
+        <v>6.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46057.64583333334</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="N22" t="n">
         <v>5</v>
       </c>
-      <c r="N22" t="n">
-        <v>11.5</v>
-      </c>
       <c r="O22" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="T22" t="n">
-        <v>2.34</v>
+        <v>2.72</v>
       </c>
       <c r="U22" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>3.62</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.3</v>
+        <v>4.04</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O23" t="n">
-        <v>3.39</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S23" t="n">
         <v>2.69</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.81</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
         <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.4</v>
       </c>
-      <c r="N24" t="n">
+      <c r="T24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.9</v>
       </c>
-      <c r="O24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE24" t="n">
+      <c r="AF24" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF24" t="n">
-        <v>2</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.17</v>
+        <v>3.4</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,61 +3396,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.88</v>
+        <v>3.38</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="O25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.15</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.22</v>
-      </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2.69</v>
       </c>
       <c r="R25" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W25" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC25" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
         <v>1.75</v>
@@ -3459,10 +3459,10 @@
         <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3515,19 +3515,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.1</v>
+        <v>4.85</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O26" t="n">
         <v>5.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
         <v>1.95</v>
@@ -3542,13 +3542,13 @@
         <v>2.32</v>
       </c>
       <c r="U26" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V26" t="n">
         <v>5.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
@@ -3563,25 +3563,25 @@
         <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AE26" t="n">
         <v>1.67</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG26" t="n">
         <v>2.45</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46057.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>7.25</v>
       </c>
       <c r="O27" t="n">
-        <v>2.77</v>
+        <v>1.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="T27" t="n">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>7.25</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.85</v>
+        <v>2.77</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.63</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
         <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
         <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
         <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
         <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>2.78</v>
+        <v>3.45</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
         <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V30" t="n">
         <v>7.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.24</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>5.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.81</v>
+        <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>3.64</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4.62</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>5.24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="T7" t="n">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.98</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>2.73</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.39</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.54</v>
+        <v>3.81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="N8" t="n">
-        <v>2.74</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>4.62</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="U8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.39</v>
       </c>
-      <c r="V8" t="n">
-        <v>6</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="M13" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="M22" t="n">
-        <v>3.94</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="O22" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="P22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.72</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.62</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.04</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="U23" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
         <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
         <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.17</v>
+        <v>2.15</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.14</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>11.5</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>2.69</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="U24" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>4.95</v>
+        <v>6.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>3.48</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>4.04</v>
       </c>
       <c r="M25" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.69</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.81</v>
-      </c>
       <c r="T25" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF25" t="n">
         <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="M27" t="n">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>7.25</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.85</v>
+        <v>2.77</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V27" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.63</v>
+        <v>1.64</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>7.25</v>
       </c>
       <c r="O28" t="n">
-        <v>2.77</v>
+        <v>1.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="T28" t="n">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.78</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
         <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
         <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
         <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
         <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R30" t="n">
         <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T30" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
         <v>7.5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>5.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.85</v>
+        <v>2.21</v>
       </c>
       <c r="T5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>11</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2.73</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AB5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.39</v>
       </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.24</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.21</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="U7" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.05</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>5.75</v>
       </c>
       <c r="O16" t="n">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>5.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.38</v>
       </c>
-      <c r="V16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.42</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>5.75</v>
+        <v>1.29</v>
       </c>
       <c r="O17" t="n">
-        <v>1.75</v>
+        <v>7.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.4</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="M22" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="N22" t="n">
         <v>5</v>
       </c>
-      <c r="N22" t="n">
-        <v>11.5</v>
-      </c>
       <c r="O22" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.25</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH22" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,61 +3158,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.94</v>
+        <v>3.38</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.15</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>2.69</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="T23" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB23" t="n">
-        <v>2</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
         <v>1.75</v>
@@ -3221,10 +3221,10 @@
         <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.3</v>
+        <v>4.04</v>
       </c>
       <c r="M24" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S24" t="n">
         <v>2.69</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.81</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF24" t="n">
         <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.04</v>
+        <v>1.14</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>11.5</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.45</v>
+        <v>8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH25" t="n">
         <v>3.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.24</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S5" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>5.85</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O6" t="n">
         <v>2.4</v>
       </c>
-      <c r="M6" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.1</v>
-      </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>5.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.81</v>
+        <v>2.54</v>
       </c>
       <c r="M9" t="n">
-        <v>3.64</v>
+        <v>3.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>2.74</v>
       </c>
       <c r="O9" t="n">
-        <v>4.62</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="V9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="O13" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>3.21</v>
+        <v>3.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AC13" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="M14" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="N14" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="T14" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.3</v>
+        <v>4.04</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S23" t="n">
         <v>2.69</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.81</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="V23" t="n">
-        <v>6.65</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
         <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF23" t="n">
         <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.04</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P24" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="R24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.37</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W24" t="n">
         <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
         <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>1.29</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>7.25</v>
       </c>
       <c r="O27" t="n">
-        <v>2.77</v>
+        <v>1.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="T27" t="n">
-        <v>3.08</v>
+        <v>2.57</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>7.25</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.85</v>
+        <v>2.77</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.63</v>
+        <v>1.64</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.24</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.2</v>
+        <v>5.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.81</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>3.64</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>4.62</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>5.24</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="T8" t="n">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.98</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>2.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.39</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.54</v>
+        <v>3.81</v>
       </c>
       <c r="M9" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>4.62</v>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.39</v>
       </c>
-      <c r="V9" t="n">
-        <v>6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>4.34</v>
       </c>
       <c r="M13" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC13" t="n">
         <v>5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2694,16 +2694,16 @@
         <v>6.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="R19" t="n">
         <v>1.45</v>
       </c>
       <c r="S19" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
         <v>3.32</v>
@@ -2721,22 +2721,22 @@
         <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
         <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
         <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.88</v>
+        <v>4.02</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
         <v>2.09</v>
@@ -2745,10 +2745,10 @@
         <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46057.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.04</v>
+        <v>3.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="N23" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.37</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W23" t="n">
         <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
         <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.3</v>
+        <v>1.14</v>
       </c>
       <c r="M24" t="n">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>11.5</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.69</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V24" t="n">
-        <v>6.65</v>
+        <v>4.95</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.14</v>
+        <v>4.04</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>11.5</v>
+        <v>1.75</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>8</v>
+        <v>2.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3.4</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V25" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.75</v>
-      </c>
       <c r="AA25" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>3.4</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3640,7 +3640,7 @@
         <v>4.45</v>
       </c>
       <c r="N27" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
         <v>1.85</v>
@@ -3655,49 +3655,49 @@
         <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="T27" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
         <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE27" t="n">
         <v>1.91</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
         <v>2.63</v>
@@ -3753,25 +3753,25 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
         <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="O28" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
         <v>2.88</v>
@@ -3783,43 +3783,43 @@
         <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W28" t="n">
         <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.54</v>
+        <v>3.63</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
         <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
         <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O29" t="n">
         <v>2.6</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.45</v>
-      </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
         <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
         <v>1.85</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.14</v>
+        <v>2.92</v>
       </c>
       <c r="M30" t="n">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>2.47</v>
       </c>
       <c r="O30" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U30" t="n">
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>8.44</v>
+        <v>7.75</v>
       </c>
       <c r="O31" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>8.31</v>
+        <v>7.5</v>
       </c>
       <c r="R31" t="n">
         <v>1.33</v>
@@ -4149,25 +4149,25 @@
         <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AA31" t="n">
         <v>1.76</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AF31" t="n">
         <v>1.73</v>
@@ -4229,28 +4229,28 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="M32" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="N32" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="O32" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
         <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T32" t="n">
         <v>2.94</v>
@@ -4262,25 +4262,25 @@
         <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD32" t="n">
         <v>1.25</v>
@@ -4289,7 +4289,7 @@
         <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AG32" t="n">
         <v>1.33</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="M6" t="n">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.85</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.17</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>3.81</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>3.64</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>4.62</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.24</v>
+        <v>2.26</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>2.21</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>2.53</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>3.98</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.81</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.64</v>
+        <v>2.87</v>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>4.62</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>2.13</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.98</v>
+        <v>2.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.69</v>
+        <v>2.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.69</v>
+        <v>5.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
         <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
         <v>4.8</v>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.55</v>
@@ -1992,19 +1992,19 @@
         <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="U13" t="n">
         <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y13" t="n">
         <v>1.46</v>
@@ -2016,19 +2016,19 @@
         <v>2.52</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD13" t="n">
         <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
         <v>1.31</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
         <v>2.53</v>
@@ -2578,13 +2578,13 @@
         <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>4.39</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="T18" t="n">
         <v>2.95</v>
@@ -2593,7 +2593,7 @@
         <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="W18" t="n">
         <v>1.09</v>
@@ -2602,34 +2602,34 @@
         <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46057.58333333334</v>
@@ -2682,70 +2682,70 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.57</v>
+        <v>5.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O19" t="n">
-        <v>6.26</v>
+        <v>5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T19" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
         <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
         <v>2.74</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
         <v>1.61</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="AD19" t="n">
         <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="AF19" t="n">
         <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="n">
         <v>1.09</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="M22" t="n">
         <v>3.94</v>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="O22" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q22" t="n">
         <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V22" t="n">
         <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA22" t="n">
         <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC22" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE22" t="n">
         <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
         <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>5.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>9.35</v>
       </c>
       <c r="O23" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.69</v>
+        <v>5.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="V23" t="n">
-        <v>6.65</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.14</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>11.5</v>
+        <v>1.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>8</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="U24" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>1.91</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.4</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.04</v>
+        <v>3.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
         <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3515,25 +3515,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.85</v>
+        <v>6.4</v>
       </c>
       <c r="M26" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="N26" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
         <v>3.3</v>
@@ -3542,13 +3542,13 @@
         <v>2.32</v>
       </c>
       <c r="U26" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V26" t="n">
         <v>5.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
@@ -3557,13 +3557,13 @@
         <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
         <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
         <v>2.5</v>
@@ -3572,7 +3572,7 @@
         <v>1.44</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
         <v>2.1</v>
@@ -3581,7 +3581,7 @@
         <v>2.45</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46057.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,28 +3872,28 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>2.47</v>
       </c>
       <c r="O29" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="T29" t="n">
         <v>3.04</v>
@@ -3902,34 +3902,34 @@
         <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF29" t="n">
         <v>1.85</v>
@@ -3938,7 +3938,7 @@
         <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,28 +3991,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.92</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T30" t="n">
         <v>3.04</v>
@@ -4021,34 +4021,34 @@
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
@@ -4057,7 +4057,7 @@
         <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="N6" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.36</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AC6" t="n">
-        <v>3.3</v>
+        <v>5.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O9" t="n">
         <v>2.4</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.1</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>5.24</v>
       </c>
       <c r="R9" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
         <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.94</v>
+        <v>5.25</v>
       </c>
       <c r="N22" t="n">
-        <v>5.14</v>
+        <v>9.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="P22" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V22" t="n">
         <v>5</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.5</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.3</v>
       </c>
-      <c r="M23" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N23" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z23" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.4</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.38</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
         <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>1.63</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.94</v>
       </c>
       <c r="N25" t="n">
-        <v>1.95</v>
+        <v>5.14</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="T25" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,28 +3872,28 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.92</v>
+        <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.47</v>
+        <v>3.4</v>
       </c>
       <c r="O29" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
         <v>3.04</v>
@@ -3902,34 +3902,34 @@
         <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
         <v>1.85</v>
@@ -3938,7 +3938,7 @@
         <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,28 +3991,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N30" t="n">
-        <v>3.4</v>
+        <v>2.47</v>
       </c>
       <c r="O30" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="T30" t="n">
         <v>3.04</v>
@@ -4021,34 +4021,34 @@
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
@@ -4057,7 +4057,7 @@
         <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.3</v>
       </c>
-      <c r="M31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="Z31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG31" t="n">
         <v>1.33</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH31" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>2.99</v>
+        <v>4.5</v>
       </c>
       <c r="N32" t="n">
-        <v>3.42</v>
+        <v>7.75</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="T32" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC32" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="M6" t="n">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.85</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.17</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.85</v>
+        <v>3.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V7" t="n">
+        <v>13</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.36</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V7" t="n">
-        <v>6</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AC7" t="n">
-        <v>3.3</v>
+        <v>5.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>2.28</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.81</v>
+        <v>1.83</v>
       </c>
       <c r="M8" t="n">
-        <v>3.64</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>4.62</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>5.24</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>2.21</v>
       </c>
       <c r="T8" t="n">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.98</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>2.73</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.09</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.69</v>
+        <v>4.2</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.39</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.83</v>
+        <v>3.81</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>3.64</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>4.62</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.24</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>2.21</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="V9" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>3.98</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.06</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>5.75</v>
+        <v>1.29</v>
       </c>
       <c r="O16" t="n">
-        <v>1.75</v>
+        <v>7.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.4</v>
+        <v>1.81</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.29</v>
+        <v>5.75</v>
       </c>
       <c r="O17" t="n">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>5.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>2.73</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.38</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.42</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -2916,17 +2916,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="M21" t="n">
         <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>4.08</v>
       </c>
       <c r="O21" t="n">
         <v>2.1</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.3</v>
       </c>
-      <c r="M22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N22" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z22" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.37</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.4</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.2</v>
+        <v>1.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="N23" t="n">
-        <v>1.85</v>
+        <v>5.14</v>
       </c>
       <c r="O23" t="n">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.45</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
         <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>2.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>5.25</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>9.35</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.67</v>
+        <v>5.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE24" t="n">
         <v>2</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.63</v>
+        <v>3.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.94</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>5.14</v>
+        <v>1.95</v>
       </c>
       <c r="O25" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.1</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.42</v>
-      </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.14</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
-        <v>2.99</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>3.42</v>
+        <v>7.75</v>
       </c>
       <c r="O31" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="AA31" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC31" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.3</v>
       </c>
-      <c r="M32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R32" t="n">
+      <c r="Z32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG32" t="n">
         <v>1.33</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH32" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -668,64 +668,64 @@
         <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46057.29166666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="M3" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46057.375</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46057.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.54</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>2.74</v>
+        <v>4.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.86</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.4</v>
+        <v>3.81</v>
       </c>
       <c r="M7" t="n">
-        <v>2.87</v>
+        <v>3.64</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>4.62</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>2.53</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.17</v>
+        <v>3.98</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.83</v>
+        <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>2.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.85</v>
+        <v>2.69</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1488,77 +1488,77 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.81</v>
+        <v>2.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.64</v>
+        <v>2.87</v>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>4.62</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>3.15</v>
+        <v>2.13</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.98</v>
+        <v>2.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.69</v>
+        <v>2.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.69</v>
+        <v>5.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.91</v>
       </c>
-      <c r="O13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.81</v>
-      </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AA13" t="n">
         <v>2.38</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V13" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.52</v>
       </c>
       <c r="AB13" t="n">
         <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.9</v>
+        <v>4.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="O15" t="n">
         <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
         <v>2.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46057.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>11</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>5.75</v>
       </c>
       <c r="O16" t="n">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.81</v>
+        <v>5.4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.38</v>
       </c>
-      <c r="V16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.42</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>5.75</v>
+        <v>1.29</v>
       </c>
       <c r="O17" t="n">
-        <v>1.75</v>
+        <v>7.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.4</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.03</v>
+        <v>3.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="O20" t="n">
         <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.37</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.38</v>
       </c>
       <c r="V20" t="n">
         <v>6.75</v>
@@ -2840,34 +2840,34 @@
         <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
         <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG20" t="n">
         <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46057.64583333334</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="M21" t="n">
         <v>3.85</v>
       </c>
       <c r="N21" t="n">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
         <v>2.1</v>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="M22" t="n">
         <v>3.5</v>
@@ -3054,19 +3054,19 @@
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
         <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="T22" t="n">
         <v>2.77</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V22" t="n">
         <v>6.5</v>
@@ -3084,10 +3084,10 @@
         <v>3.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC22" t="n">
         <v>3.3</v>
@@ -3099,13 +3099,13 @@
         <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.63</v>
+        <v>3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>5.14</v>
+        <v>2.01</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>3.92</v>
       </c>
       <c r="P23" t="n">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.96</v>
+        <v>3.24</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="N24" t="n">
-        <v>9.35</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="P24" t="n">
         <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.8</v>
+        <v>6.18</v>
       </c>
       <c r="R24" t="n">
         <v>1.28</v>
@@ -3301,10 +3301,10 @@
         <v>3.34</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="V24" t="n">
         <v>5</v>
@@ -3316,16 +3316,16 @@
         <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="AC24" t="n">
         <v>2.45</v>
@@ -3343,7 +3343,7 @@
         <v>1.11</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.3</v>
+        <v>1.63</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.95</v>
       </c>
-      <c r="O25" t="n">
-        <v>4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="M26" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -3530,58 +3530,58 @@
         <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="T26" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U26" t="n">
         <v>1.54</v>
       </c>
       <c r="V26" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.45</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46057.70833333334</v>
@@ -3634,25 +3634,25 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
-        <v>4.45</v>
+        <v>4.59</v>
       </c>
       <c r="N27" t="n">
         <v>7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
         <v>3.04</v>
@@ -3664,31 +3664,31 @@
         <v>1.45</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
         <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AB27" t="n">
         <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
         <v>1.91</v>
@@ -3697,7 +3697,7 @@
         <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AH27" t="n">
         <v>2.63</v>
@@ -3756,28 +3756,28 @@
         <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="N28" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="T28" t="n">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="U28" t="n">
         <v>1.35</v>
@@ -3789,34 +3789,34 @@
         <v>1.03</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE28" t="n">
         <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH28" t="n">
         <v>1.62</v>
@@ -3872,31 +3872,31 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
         <v>1.33</v>
@@ -3908,31 +3908,31 @@
         <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE29" t="n">
         <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
         <v>1.33</v>
@@ -3991,64 +3991,64 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="M30" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="O30" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
         <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="T30" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="W30" t="n">
         <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
         <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AA30" t="n">
         <v>2.23</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N31" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
         <v>1.23</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC31" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4229,28 +4229,28 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="N32" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
         <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
         <v>2.94</v>
@@ -4259,37 +4259,37 @@
         <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="W32" t="n">
         <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC32" t="n">
         <v>3.38</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE32" t="n">
         <v>1.8</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
         <v>1.33</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>5.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>6.65</v>
+        <v>9.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.14</v>
+        <v>5.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="N6" t="n">
-        <v>4.75</v>
+        <v>3.26</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE6" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1254,31 +1254,31 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.81</v>
+        <v>4.03</v>
       </c>
       <c r="M7" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="O7" t="n">
-        <v>4.62</v>
+        <v>4.45</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
         <v>1.46</v>
@@ -1296,31 +1296,31 @@
         <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.98</v>
+        <v>4.09</v>
       </c>
       <c r="AA7" t="n">
         <v>1.69</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
         <v>2.69</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.83</v>
+        <v>2.69</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>2.53</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.24</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.25</v>
       </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.73</v>
+        <v>2.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3.1</v>
       </c>
-      <c r="P9" t="n">
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V9" t="n">
-        <v>13</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1611,40 +1611,40 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>5.82</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.91</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.11</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -1653,31 +1653,31 @@
         <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="n">
         <v>1.57</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46057.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>4.35</v>
       </c>
       <c r="M12" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.7</v>
       </c>
-      <c r="N12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="M13" t="n">
         <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
         <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.43</v>
+        <v>2.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="AB13" t="n">
         <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.91</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4.8</v>
+        <v>2.53</v>
       </c>
       <c r="P14" t="n">
         <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.5</v>
+        <v>6.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="T14" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>1.84</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2206,67 +2206,67 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
         <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.43</v>
+        <v>2.52</v>
       </c>
       <c r="O15" t="n">
         <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
         <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
         <v>2.01</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.88</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
         <v>1.5</v>
@@ -2325,40 +2325,40 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="N16" t="n">
-        <v>5.75</v>
+        <v>7.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
         <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="V16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
@@ -2367,31 +2367,31 @@
         <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>5.79</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
         <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>3.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2444,28 +2444,28 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N17" t="n">
         <v>1.29</v>
       </c>
       <c r="O17" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
         <v>2.81</v>
@@ -2474,37 +2474,37 @@
         <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W17" t="n">
         <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
         <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AA17" t="n">
         <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
         <v>2.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
         <v>1.18</v>
@@ -2569,28 +2569,28 @@
         <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="P18" t="n">
         <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
         <v>6.1</v>
@@ -2599,37 +2599,37 @@
         <v>1.09</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
         <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AE18" t="n">
         <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AG18" t="n">
         <v>1.31</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46057.58333333334</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.39</v>
+        <v>4.48</v>
       </c>
       <c r="M19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="T19" t="n">
         <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
         <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
         <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
         <v>1.65</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46057.625</v>
@@ -2810,7 +2810,7 @@
         <v>2.05</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>4.09</v>
       </c>
       <c r="P20" t="n">
         <v>2.15</v>
@@ -2849,7 +2849,7 @@
         <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>3.3</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
         <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.4</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.01</v>
+        <v>7.65</v>
       </c>
       <c r="O23" t="n">
-        <v>3.92</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.67</v>
+        <v>6.18</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>3.71</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="M24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q24" t="n">
         <v>5</v>
       </c>
-      <c r="N24" t="n">
-        <v>9</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>6.18</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.45</v>
+        <v>2.99</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.63</v>
+        <v>3.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>5.31</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3527,49 +3527,49 @@
         <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V26" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="W26" t="n">
         <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
         <v>2.45</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE26" t="n">
         <v>1.73</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>4.03</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>1.72</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>4.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.49</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>3.12</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.25</v>
       </c>
-      <c r="V5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="M6" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>3.26</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>2.62</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.1</v>
+        <v>5.49</v>
       </c>
       <c r="R6" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="T6" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.65</v>
+        <v>5.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.03</v>
+        <v>2.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>2.53</v>
       </c>
       <c r="O7" t="n">
-        <v>4.45</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.09</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="N8" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>3.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V8" t="n">
-        <v>6.75</v>
+        <v>9.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>5.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.35</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>4.4</v>
+        <v>2.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.7</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.58</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.14</v>
+        <v>1.84</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="O13" t="n">
         <v>3.5</v>
@@ -1983,22 +1983,22 @@
         <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
@@ -2007,34 +2007,34 @@
         <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
         <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
         <v>1.72</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="n">
         <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2325,19 +2325,19 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>5.67</v>
+        <v>5.25</v>
       </c>
       <c r="N16" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O16" t="n">
         <v>1.73</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q16" t="n">
         <v>7</v>
@@ -2346,13 +2346,13 @@
         <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="V16" t="n">
         <v>4.1</v>
@@ -2367,13 +2367,13 @@
         <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.79</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
         <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="AC16" t="n">
         <v>2</v>
@@ -2382,16 +2382,16 @@
         <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.53</v>
+        <v>3.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2682,31 +2682,31 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.48</v>
+        <v>4.11</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="P19" t="n">
         <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U19" t="n">
         <v>1.26</v>
@@ -2715,40 +2715,40 @@
         <v>9.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
         <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
         <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46057.625</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
-        <v>7.65</v>
+        <v>5.31</v>
       </c>
       <c r="O23" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.18</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.45</v>
+        <v>2.99</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.71</v>
+        <v>2.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.63</v>
+        <v>3.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>5.31</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P24" t="n">
         <v>2.1</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.75</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.08</v>
+        <v>7.65</v>
       </c>
       <c r="O25" t="n">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.62</v>
+        <v>6.18</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>3.34</v>
       </c>
       <c r="T25" t="n">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V25" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>3.71</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1012,77 +1012,77 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.03</v>
+        <v>2.69</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.72</v>
+        <v>2.53</v>
       </c>
       <c r="O5" t="n">
-        <v>4.45</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U5" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8</v>
+        <v>6.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.09</v>
+        <v>3.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.83</v>
+        <v>4.03</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
-        <v>2.62</v>
+        <v>4.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.49</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>2.26</v>
+        <v>3.12</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.25</v>
       </c>
-      <c r="V6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.98</v>
+        <v>1.16</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="N7" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>3.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
-        <v>6.75</v>
+        <v>9.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>5.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.36</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>2.77</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>3.26</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.26</v>
+        <v>2.22</v>
       </c>
       <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>5.49</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.5</v>
+        <v>5.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.08</v>
+        <v>5.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.98</v>
+        <v>2.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.54</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.36</v>
       </c>
-      <c r="V22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.63</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>5.31</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.1</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.06</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3283,7 +3283,7 @@
         <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
         <v>4.33</v>
@@ -3295,22 +3295,22 @@
         <v>2.62</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
         <v>2.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
@@ -3411,7 +3411,7 @@
         <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.18</v>
+        <v>6.38</v>
       </c>
       <c r="R25" t="n">
         <v>1.28</v>
@@ -3420,10 +3420,10 @@
         <v>3.34</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U25" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="V25" t="n">
         <v>5</v>
@@ -3435,7 +3435,7 @@
         <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
         <v>4.75</v>
@@ -3444,10 +3444,10 @@
         <v>1.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AD25" t="n">
         <v>1.5</v>
@@ -3456,13 +3456,13 @@
         <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
         <v>1.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3515,22 +3515,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="M26" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="N26" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
@@ -3542,7 +3542,7 @@
         <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V26" t="n">
         <v>5.05</v>
@@ -3557,7 +3557,7 @@
         <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA26" t="n">
         <v>1.61</v>
@@ -3566,16 +3566,16 @@
         <v>2.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD26" t="n">
         <v>1.44</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
         <v>1.18</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -668,13 +668,13 @@
         <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.16</v>
+        <v>3.24</v>
       </c>
       <c r="P2" t="n">
         <v>1.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.7</v>
@@ -698,34 +698,34 @@
         <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Z2" t="n">
         <v>2.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AB2" t="n">
         <v>1.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AD2" t="n">
         <v>1.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AF2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.47</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46057.29166666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="M3" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="N3" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.85</v>
+        <v>5.48</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="T3" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="U3" t="n">
         <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y3" t="n">
         <v>1.72</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46057.375</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="N4" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.95</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="V4" t="n">
         <v>13</v>
@@ -933,37 +933,37 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.95</v>
+        <v>4.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46057.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.69</v>
+        <v>1.65</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>2.53</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
         <v>3.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.03</v>
+        <v>2.36</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>2.77</v>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>3.26</v>
       </c>
       <c r="O6" t="n">
-        <v>4.45</v>
+        <v>3.26</v>
       </c>
       <c r="P6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE6" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.09</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="M7" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
-        <v>3.26</v>
+        <v>2.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.11</v>
+        <v>2.62</v>
       </c>
       <c r="T7" t="n">
-        <v>3.92</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>9.4</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.19</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC7" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>4.03</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>2.22</v>
+        <v>4.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="V8" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>4.09</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>1.16</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N11" t="n">
         <v>2.7</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.8</v>
-      </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.72</v>
+        <v>3.69</v>
       </c>
       <c r="M13" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="T13" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="N14" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.11</v>
+        <v>4.24</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O19" t="n">
         <v>4.5</v>
@@ -2697,34 +2697,34 @@
         <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T19" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA19" t="n">
         <v>2.37</v>
@@ -2733,19 +2733,19 @@
         <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.79</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
         <v>1.16</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>5.35</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.1</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="T22" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.06</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>7.65</v>
       </c>
       <c r="O23" t="n">
-        <v>3.98</v>
+        <v>1.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.7</v>
+        <v>6.38</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>2.77</v>
+        <v>3.34</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.29</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>2.39</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.24</v>
+        <v>2.44</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.29</v>
+        <v>3.73</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.75</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="AA24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>3.75</v>
       </c>
       <c r="M25" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>7.65</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.38</v>
+        <v>2.62</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>2.29</v>
+        <v>2.81</v>
       </c>
       <c r="U25" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>6.65</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.39</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3637,25 +3637,25 @@
         <v>1.44</v>
       </c>
       <c r="M27" t="n">
-        <v>4.59</v>
+        <v>4.45</v>
       </c>
       <c r="N27" t="n">
         <v>7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="R27" t="n">
         <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="T27" t="n">
         <v>2.56</v>
@@ -3673,22 +3673,22 @@
         <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
         <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE27" t="n">
         <v>1.91</v>
@@ -3697,10 +3697,10 @@
         <v>1.8</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3753,58 +3753,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="O28" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
         <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="T28" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
         <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.54</v>
+        <v>3.88</v>
       </c>
       <c r="AD28" t="n">
         <v>1.25</v>
@@ -3813,10 +3813,10 @@
         <v>1.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
         <v>1.62</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="M29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O29" t="n">
         <v>3.3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.82</v>
       </c>
       <c r="P29" t="n">
         <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>3.26</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T29" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
         <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA29" t="n">
         <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.86</v>
+        <v>4.04</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.95</v>
       </c>
       <c r="AG29" t="n">
         <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.83333333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,64 +3991,64 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U30" t="n">
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
@@ -4057,7 +4057,7 @@
         <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>2.35</v>
       </c>
       <c r="M31" t="n">
-        <v>4.6</v>
+        <v>3.18</v>
       </c>
       <c r="N31" t="n">
-        <v>8.5</v>
+        <v>2.91</v>
       </c>
       <c r="O31" t="n">
-        <v>1.8</v>
+        <v>2.69</v>
       </c>
       <c r="P31" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="S31" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
         <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="AE31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG31" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.93</v>
+        <v>1.57</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="N32" t="n">
-        <v>3.32</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>2.61</v>
+        <v>1.75</v>
       </c>
       <c r="P32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA32" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>5.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V5" t="n">
-        <v>7.1</v>
+        <v>9.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.5</v>
+        <v>5.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.36</v>
+        <v>4.03</v>
       </c>
       <c r="M6" t="n">
-        <v>2.77</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>3.26</v>
+        <v>1.72</v>
       </c>
       <c r="O6" t="n">
-        <v>3.26</v>
+        <v>4.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.66</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.69</v>
+        <v>2.36</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="N7" t="n">
-        <v>2.53</v>
+        <v>3.26</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>3.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="V7" t="n">
-        <v>6.75</v>
+        <v>9.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.03</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.2</v>
+        <v>5.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.03</v>
+        <v>2.69</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>2.53</v>
       </c>
       <c r="O8" t="n">
-        <v>4.45</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.09</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="P9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q9" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>2.68</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>3.54</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.35</v>
+        <v>3.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.84</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
@@ -2004,16 +2004,16 @@
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AB13" t="n">
         <v>1.43</v>
@@ -2034,7 +2034,7 @@
         <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.73</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
         <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="N16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="O16" t="n">
-        <v>1.73</v>
+        <v>8.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>7</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8</v>
+        <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>2.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>4.1</v>
+        <v>6.55</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>3.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>3.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.12</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>9.699999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="N17" t="n">
-        <v>1.29</v>
+        <v>6.6</v>
       </c>
       <c r="O17" t="n">
-        <v>8.5</v>
+        <v>1.67</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
-        <v>6.55</v>
+        <v>4.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.18</v>
+        <v>6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.18</v>
+        <v>2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>3.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -2688,28 +2688,28 @@
         <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>4.5</v>
+        <v>5.13</v>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="T19" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
         <v>9</v>
@@ -2721,28 +2721,28 @@
         <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="AB19" t="n">
         <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.6</v>
+        <v>4.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
         <v>1.29</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="M22" t="n">
         <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="P22" t="n">
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W22" t="n">
         <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC22" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.29</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>7.65</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.7</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH23" t="n">
-        <v>3.73</v>
+        <v>1.29</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.75</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="N25" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V25" t="n">
+        <v>5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2</v>
       </c>
-      <c r="O25" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>3.73</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.44</v>
       </c>
-      <c r="M27" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="N27" t="n">
-        <v>7</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.33</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.45</v>
-      </c>
       <c r="V27" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE27" t="n">
+      <c r="AF27" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>3.22</v>
+        <v>4.45</v>
       </c>
       <c r="N28" t="n">
-        <v>3.46</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2.8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V28" t="n">
-        <v>8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>2.01</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U2" t="n">
         <v>1.15</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="M3" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
         <v>5.48</v>
@@ -808,7 +808,7 @@
         <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -823,10 +823,10 @@
         <v>1.98</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
         <v>4.9</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="M4" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
@@ -915,7 +915,7 @@
         <v>2.93</v>
       </c>
       <c r="R4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
         <v>2.03</v>
@@ -930,22 +930,22 @@
         <v>13</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AA4" t="n">
         <v>3.08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
         <v>4.75</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="P5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q5" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1131,77 +1131,77 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.03</v>
+        <v>2.64</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="O6" t="n">
-        <v>4.45</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.29</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1254,49 +1254,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="M7" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="N7" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S7" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="T7" t="n">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="U7" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V7" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y7" t="n">
         <v>1.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AA7" t="n">
         <v>3</v>
@@ -1305,22 +1305,22 @@
         <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.65</v>
+        <v>5.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.69</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="AD8" t="n">
         <v>1.38</v>
       </c>
-      <c r="V8" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
+      <c r="AE8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="O9" t="n">
-        <v>2.22</v>
+        <v>2.64</v>
       </c>
       <c r="P9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="AA9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N10" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="O10" t="n">
-        <v>5.5</v>
+        <v>6.28</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
         <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
         <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AF10" t="n">
         <v>2.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46057.48958333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
         <v>3.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="T12" t="n">
-        <v>3.68</v>
+        <v>3.21</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>9.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
@@ -1888,7 +1888,7 @@
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="n">
         <v>2.28</v>
@@ -1897,19 +1897,19 @@
         <v>2.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD12" t="n">
         <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AG12" t="n">
         <v>1.36</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>2.73</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.35</v>
+        <v>5.5</v>
       </c>
       <c r="R14" t="n">
         <v>1.63</v>
@@ -2111,7 +2111,7 @@
         <v>2.13</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="U14" t="n">
         <v>1.19</v>
@@ -2123,37 +2123,37 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>3.76</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
         <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
         <v>3.22</v>
@@ -2245,22 +2245,22 @@
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>3.96</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE15" t="n">
         <v>1.91</v>
@@ -2269,7 +2269,7 @@
         <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
         <v>1.4</v>
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>9.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="O16" t="n">
         <v>8.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
         <v>1.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
         <v>2.77</v>
       </c>
       <c r="T16" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
         <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.29</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
         <v>2.25</v>
@@ -2388,10 +2388,10 @@
         <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>3.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="N17" t="n">
         <v>6.6</v>
@@ -2456,10 +2456,10 @@
         <v>1.67</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="R17" t="n">
         <v>1.18</v>
@@ -2468,22 +2468,22 @@
         <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V17" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z17" t="n">
         <v>6</v>
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
         <v>2.15</v>
@@ -2581,16 +2581,16 @@
         <v>4.4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.48</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
         <v>6.1</v>
@@ -2602,34 +2602,34 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46057.58333333334</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.24</v>
+        <v>4.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O19" t="n">
         <v>5.13</v>
@@ -2709,7 +2709,7 @@
         <v>3.32</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
         <v>9</v>
@@ -2718,10 +2718,10 @@
         <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
         <v>2.56</v>
@@ -2742,7 +2742,7 @@
         <v>2.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG19" t="n">
         <v>1.29</v>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
         <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T20" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
         <v>6.75</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46057.64583333334</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="M21" t="n">
         <v>3.85</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>4.33</v>
+        <v>4.09</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>6.65</v>
+        <v>6.7</v>
       </c>
       <c r="W22" t="n">
         <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
         <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
         <v>3.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>13</v>
       </c>
       <c r="O23" t="n">
-        <v>3.98</v>
+        <v>1.64</v>
       </c>
       <c r="P23" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.29</v>
+        <v>3.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>5.35</v>
+        <v>2.12</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>4.54</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.94</v>
+        <v>2.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="W24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.06</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
         <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>7.65</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.38</v>
+        <v>5.89</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.29</v>
+        <v>2.77</v>
       </c>
       <c r="U25" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W25" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.73</v>
+        <v>2.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="M26" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="R26" t="n">
         <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="U26" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="V26" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X26" t="n">
         <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD26" t="n">
         <v>1.44</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG26" t="n">
         <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46057.70833333334</v>
@@ -3593,27 +3593,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,80 +3630,80 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3.46</v>
+        <v>1.95</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T27" t="n">
         <v>3.5</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y27" t="n">
         <v>1.44</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.31</v>
-      </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.88</v>
+        <v>4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46057.79166666666</v>
+        <v>46057.75</v>
       </c>
     </row>
     <row r="28">
@@ -3753,46 +3753,46 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="N28" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q28" t="n">
         <v>7</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>6.6</v>
-      </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="T28" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V28" t="n">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
         <v>3.75</v>
@@ -3801,25 +3801,25 @@
         <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,76 +3872,76 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="M29" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="O29" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="T29" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB29" t="n">
         <v>1.66</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.04</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
         <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI29" s="3" t="n">
-        <v>46057.83333333334</v>
+        <v>46057.79166666666</v>
       </c>
     </row>
     <row r="30">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,46 +3991,46 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="M30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O30" t="n">
         <v>3.3</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.4</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.85</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T30" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U30" t="n">
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
         <v>2.9</v>
@@ -4042,22 +4042,22 @@
         <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD30" t="n">
         <v>1.22</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF30" t="n">
         <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,76 +4110,76 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="M31" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="N31" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z31" t="n">
         <v>2.9</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3</v>
-      </c>
       <c r="AA31" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AI31" s="3" t="n">
-        <v>46057.89583333334</v>
+        <v>46057.83333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4229,16 +4229,16 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="M32" t="n">
-        <v>4.95</v>
+        <v>4.65</v>
       </c>
       <c r="N32" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="O32" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="P32" t="n">
         <v>2.45</v>
@@ -4247,49 +4247,49 @@
         <v>7.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="T32" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V32" t="n">
-        <v>6.15</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
         <v>1.18</v>
@@ -4298,6 +4298,125 @@
         <v>3.1</v>
       </c>
       <c r="AI32" s="3" t="n">
+        <v>46057.89583333334</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI33" s="3" t="n">
         <v>46057.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -668,10 +668,10 @@
         <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
         <v>4.8</v>
@@ -689,7 +689,7 @@
         <v>1.15</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W2" t="n">
         <v>1.01</v>
@@ -698,16 +698,16 @@
         <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
         <v>6.45</v>
@@ -725,7 +725,7 @@
         <v>1.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46057.29166666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>5.48</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="S3" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="T3" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="U3" t="n">
         <v>1.14</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.9</v>
+        <v>6.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46057.375</v>
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="N4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.05</v>
       </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.03</v>
-      </c>
       <c r="T4" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="V4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W4" t="n">
         <v>1.01</v>
@@ -936,34 +936,34 @@
         <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.75</v>
+        <v>6.45</v>
       </c>
       <c r="AD4" t="n">
         <v>1.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46057.41666666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>4.03</v>
       </c>
       <c r="M7" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>1.72</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>2.07</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>4.05</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.16</v>
-      </c>
-      <c r="V7" t="n">
-        <v>13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.46</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.03</v>
+        <v>2.16</v>
       </c>
       <c r="M8" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.7</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.72</v>
-      </c>
       <c r="O8" t="n">
-        <v>4.45</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>3.12</v>
+        <v>2.07</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>3.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.09</v>
+        <v>2.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.69</v>
+        <v>5.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.66</v>
+        <v>2.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M9" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="N9" t="n">
-        <v>4.55</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.85</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.35</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
         <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="M13" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>2.73</v>
+        <v>4.85</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AB13" t="n">
         <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>4.85</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>2.45</v>
+        <v>4.99</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>3.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="S14" t="n">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="T14" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="U14" t="n">
         <v>1.19</v>
       </c>
       <c r="V14" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
         <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.199999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.33</v>
+        <v>6.6</v>
       </c>
       <c r="O16" t="n">
-        <v>8.5</v>
+        <v>1.67</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.75</v>
+        <v>6.4</v>
       </c>
       <c r="R16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.29</v>
       </c>
-      <c r="M17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>3.1</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.25</v>
+        <v>1.27</v>
       </c>
       <c r="M22" t="n">
-        <v>3.33</v>
+        <v>5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
-        <v>4.09</v>
+        <v>1.64</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="T22" t="n">
-        <v>2.85</v>
+        <v>2.39</v>
       </c>
       <c r="U22" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="V22" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>3.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.27</v>
+        <v>3.25</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>3.33</v>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.64</v>
+        <v>4.09</v>
       </c>
       <c r="P23" t="n">
-        <v>2.77</v>
+        <v>2.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.359999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.3</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.7</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3630,17 +3630,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.7</v>
+        <v>4.53</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O27" t="n">
         <v>4.6</v>
@@ -3652,28 +3652,28 @@
         <v>2.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S27" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U27" t="n">
         <v>1.22</v>
       </c>
       <c r="V27" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
         <v>1.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
         <v>2.4</v>
@@ -3682,7 +3682,7 @@
         <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC27" t="n">
         <v>4.8</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>7.98</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V28" t="n">
         <v>7</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.65</v>
-      </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="AA28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AF28" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.97</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>7.98</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="T29" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.62</v>
+        <v>2.97</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.79166666666</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,48 +880,48 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="M4" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
         <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="P4" t="n">
         <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="R4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S4" t="n">
         <v>2.05</v>
       </c>
       <c r="T4" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="U4" t="n">
         <v>1.14</v>
@@ -930,40 +930,40 @@
         <v>11</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="AD4" t="n">
         <v>1.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG4" t="n">
         <v>1.43</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46057.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>2.73</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.56</v>
+        <v>2.07</v>
       </c>
       <c r="T5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V5" t="n">
+        <v>13</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA5" t="n">
         <v>2.88</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.37</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.03</v>
+        <v>2.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.09</v>
+        <v>2.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1369,77 +1369,77 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.16</v>
+        <v>4.03</v>
       </c>
       <c r="M8" t="n">
-        <v>2.73</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>1.72</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>2.07</v>
+        <v>3.12</v>
       </c>
       <c r="T8" t="n">
-        <v>3.9</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.16</v>
-      </c>
-      <c r="V8" t="n">
-        <v>13</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1733,10 +1733,10 @@
         <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2206,61 +2206,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="O15" t="n">
-        <v>3.76</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
         <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
         <v>3.22</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
         <v>1.91</v>
@@ -2269,10 +2269,10 @@
         <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46057.54166666666</v>
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>3.53</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
         <v>2.63</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="T20" t="n">
         <v>2.9</v>
@@ -2831,7 +2831,7 @@
         <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>6.75</v>
+        <v>7.3</v>
       </c>
       <c r="W20" t="n">
         <v>1.03</v>
@@ -2840,31 +2840,31 @@
         <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
         <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AD20" t="n">
         <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AH20" t="n">
         <v>1.3</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="M5" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="R5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V5" t="n">
+        <v>12</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.6</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V5" t="n">
-        <v>13</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>2.69</v>
       </c>
       <c r="M6" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
         <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="T6" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
         <v>7.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.39</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1250,77 +1250,77 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.69</v>
       </c>
-      <c r="M7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.03</v>
+        <v>2.08</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="N8" t="n">
-        <v>1.72</v>
+        <v>2.89</v>
       </c>
       <c r="O8" t="n">
-        <v>4.45</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.25</v>
+        <v>5.03</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>4.05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="V8" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.09</v>
+        <v>2.16</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.69</v>
+        <v>2.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.69</v>
+        <v>5.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.07</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.66</v>
+        <v>2.38</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA9" t="n">
         <v>2.25</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V9" t="n">
-        <v>12</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>1.56</v>
       </c>
-      <c r="Z9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1594,54 +1594,54 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="N10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="O10" t="n">
-        <v>6.28</v>
+        <v>5.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R10" t="n">
         <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="W10" t="n">
         <v>1.16</v>
@@ -1656,28 +1656,28 @@
         <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AD10" t="n">
         <v>1.75</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46057.48958333334</v>
@@ -1716,17 +1716,17 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4.85</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.51</v>
+        <v>4.99</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>3.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="S13" t="n">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="T13" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="U13" t="n">
         <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4.99</v>
+        <v>2.62</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.08</v>
+        <v>5.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2215,49 +2215,49 @@
         <v>2.36</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="T15" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
         <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AB15" t="n">
         <v>1.57</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>4.43</v>
       </c>
       <c r="AD15" t="n">
         <v>1.18</v>
@@ -2269,10 +2269,10 @@
         <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46057.54166666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.29</v>
       </c>
-      <c r="M16" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>3.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>4.8</v>
+        <v>5.15</v>
       </c>
       <c r="N17" t="n">
-        <v>1.33</v>
+        <v>7.65</v>
       </c>
       <c r="O17" t="n">
-        <v>8.5</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.75</v>
+        <v>6.53</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>4.4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="U17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.38</v>
       </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.24</v>
+        <v>2.11</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.1</v>
+        <v>1.11</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46057.5625</v>
@@ -2804,52 +2804,52 @@
         <v>3.53</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA20" t="n">
         <v>1.95</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>3.45</v>
@@ -2864,7 +2864,7 @@
         <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="n">
         <v>1.3</v>
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.53</v>
+        <v>4.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O27" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="T27" t="n">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="U27" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V27" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46057.75</v>
@@ -3753,34 +3753,34 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O28" t="n">
         <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
         <v>7</v>
@@ -3789,7 +3789,7 @@
         <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
         <v>1.36</v>
@@ -3798,10 +3798,10 @@
         <v>2.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC28" t="n">
         <v>3.9</v>
@@ -3810,16 +3810,16 @@
         <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3872,64 +3872,64 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M29" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="N29" t="n">
-        <v>7.98</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="P29" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
         <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="T29" t="n">
         <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>5.65</v>
+        <v>5.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
         <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
         <v>3.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AF29" t="n">
         <v>1.73</v>
@@ -3938,7 +3938,7 @@
         <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46057.79166666666</v>
@@ -3991,25 +3991,25 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="M30" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="O30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="S30" t="n">
         <v>2.53</v>
@@ -4021,28 +4021,28 @@
         <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
         <v>1.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z30" t="n">
         <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD30" t="n">
         <v>1.22</v>
@@ -4054,10 +4054,10 @@
         <v>1.85</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46057.83333333334</v>
@@ -4110,28 +4110,28 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="M31" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>2.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
         <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T31" t="n">
         <v>3.1</v>
@@ -4140,10 +4140,10 @@
         <v>1.32</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
         <v>1.02</v>
@@ -4155,13 +4155,13 @@
         <v>2.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD31" t="n">
         <v>1.22</v>
@@ -4229,58 +4229,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="M32" t="n">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="N32" t="n">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="R32" t="n">
         <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="T32" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U32" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V32" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD32" t="n">
         <v>1.33</v>
@@ -4351,7 +4351,7 @@
         <v>2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="N33" t="n">
         <v>2.82</v>
@@ -4360,22 +4360,22 @@
         <v>2.89</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="R33" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
         <v>6.5</v>
@@ -4387,34 +4387,34 @@
         <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z33" t="n">
         <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.44</v>
+        <v>3.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE33" t="n">
         <v>1.8</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46057.89583333334</v>

--- a/jogos_2026-02-04.xlsx
+++ b/jogos_2026-02-04.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.69</v>
+        <v>2.08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>2.89</v>
       </c>
       <c r="O6" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.2</v>
+        <v>5.03</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.73</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,99 +1228,99 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.03</v>
+        <v>2.69</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>4.45</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.09</v>
+        <v>2.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.14</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,25 +1347,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8</v>
+        <v>3.07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.89</v>
+        <v>4.67</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="T8" t="n">
-        <v>4.05</v>
+        <v>2.94</v>
       </c>
       <c r="U8" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.8</v>
+        <v>4.03</v>
       </c>
       <c r="M9" t="n">
-        <v>3.07</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4.67</v>
+        <v>1.72</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>4.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>2.39</v>
+        <v>3.12</v>
       </c>
       <c r="T9" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="V9" t="n">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>4.09</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.56</v>
+        <v>2.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.35</v>
+        <v>2.69</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.16</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46057.45833333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,25 +1704,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="M11" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.7</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3</v>
       </c>
       <c r="AB11" t="n">
         <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46057.5</v>
@@ -1832,54 +1832,54 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M12" t="n">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="N12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>3.21</v>
+        <v>3.76</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>1.04</v>
@@ -1888,34 +1888,34 @@
         <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="AD12" t="n">
         <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46057.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,99 +1942,99 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46057.5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.87</v>
+        <v>3.55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>2.82</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="U14" t="n">
         <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
         <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46057.5</v>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2311,51 +2311,51 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
         <v>4.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="P16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.38</v>
-      </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
@@ -2364,34 +2364,34 @@
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="AD16" t="n">
         <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.1</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46057.5625</v>
@@ -2427,20 +2427,20 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
         <v>3.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="P18" t="n">
         <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.4</v>
+        <v>4.47</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>2.48</v>
       </c>
       <c r="T18" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.54</v>
+        <v>2.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.05</v>
+        <v>3.79</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46057.58333333334</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.07</v>
+        <v>4.49</v>
       </c>
       <c r="M19" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O19" t="n">
-        <v>5.13</v>
+        <v>4.33</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T19" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.57</v>
+        <v>4.4</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.15</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46057.625</v>
@@ -2801,28 +2801,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.53</v>
+        <v>4.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T20" t="n">
         <v>2.81</v>
@@ -2831,16 +2831,16 @@
         <v>1.37</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W20" t="n">
         <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z20" t="n">
         <v>3.25</v>
@@ -2852,10 +2852,10 @@
         <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
         <v>1.86</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.27</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>5</v>
+        <v>3.33</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.64</v>
+        <v>4.09</v>
       </c>
       <c r="P22" t="n">
-        <v>2.77</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>9.359999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.3</v>
       </c>
-      <c r="S22" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z22" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.7</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O23" t="n">
-        <v>4.09</v>
+        <v>4.54</v>
       </c>
       <c r="P23" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T23" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="U23" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="W23" t="n">
         <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
         <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
         <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.12</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>4.54</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.5</v>
+        <v>5.89</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
         <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46057.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O25" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.89</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>3.22</v>
       </c>
       <c r="T25" t="n">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46057.69791666666</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>4.45</v>
+        <v>3.18</v>
       </c>
       <c r="N32" t="n">
-        <v>8.25</v>
+        <v>2.82</v>
       </c>
       <c r="O32" t="n">
-        <v>1.85</v>
+        <v>2.89</v>
       </c>
       <c r="P32" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>3.98</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>2.89</v>
+        <v>2.53</v>
       </c>
       <c r="T32" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="U32" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V32" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AG32" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH32" t="n">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46057.89583333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
-        <v>3.18</v>
+        <v>4.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.82</v>
+        <v>8.25</v>
       </c>
       <c r="O33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
         <v>2.89</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.53</v>
-      </c>
       <c r="T33" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="U33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.33</v>
       </c>
-      <c r="V33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE33" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46057.89583333334</v>
